--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_263_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_263_R27.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6505</v>
+        <v>3.7212</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8999</v>
+        <v>3.7824</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7506</v>
+        <v>-0.0613</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1073</v>
+        <v>2.1514</v>
       </c>
       <c r="H2" t="n">
-        <v>0.137</v>
+        <v>0.6123</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9704</v>
+        <v>1.5392</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2326</v>
+        <v>2.5483</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4166</v>
+        <v>0.4271</v>
       </c>
       <c r="L2" t="n">
-        <v>0.184</v>
+        <v>2.1212</v>
       </c>
       <c r="M2" t="n">
-        <v>1.34</v>
+        <v>-0.3969</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5536</v>
+        <v>0.1852</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7863</v>
+        <v>-0.5821</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9195</v>
+        <v>-1.0565</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1325</v>
+        <v>-0.2867</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2131</v>
+        <v>-0.7699</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.4665</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5217</v>
+        <v>2.3879</v>
       </c>
       <c r="E3" t="n">
-        <v>3.751</v>
+        <v>0.0742</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2293</v>
+        <v>2.3137</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1514</v>
+        <v>1.1073</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6123</v>
+        <v>0.137</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5392</v>
+        <v>0.9704</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5483</v>
+        <v>-0.2326</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4271</v>
+        <v>-0.4166</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1212</v>
+        <v>0.184</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3969</v>
+        <v>1.34</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1852</v>
+        <v>0.5536</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5821</v>
+        <v>0.7863</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.256</v>
+        <v>-0.3431</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3181</v>
+        <v>0.3068</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9379</v>
+        <v>-0.6499</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4665</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5528</v>
+        <v>2.1339</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3868</v>
+        <v>4.6106</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8339</v>
+        <v>-2.4768</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2508</v>
+        <v>1.2045</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5489000000000001</v>
+        <v>1.8739</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7997</v>
+        <v>-0.6694</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9943</v>
+        <v>2.3986</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5293</v>
+        <v>2.1713</v>
       </c>
       <c r="L4" t="n">
-        <v>0.465</v>
+        <v>0.2272</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2451</v>
+        <v>-1.1941</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9804</v>
+        <v>-0.2974</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2647</v>
+        <v>-0.8966</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0356</v>
+        <v>-0.7459</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5895</v>
+        <v>-0.2159</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6251</v>
+        <v>-0.53</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>0.2836</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>2.428</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2267</v>
+        <v>1.7894</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8715</v>
+        <v>2.8586</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6448</v>
+        <v>-1.0692</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2045</v>
+        <v>-0.2508</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8739</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6694</v>
+        <v>-0.7997</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3986</v>
+        <v>1.9943</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1713</v>
+        <v>1.5293</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2272</v>
+        <v>0.465</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1941</v>
+        <v>-2.2451</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2974</v>
+        <v>-0.9804</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8966</v>
+        <v>-1.2647</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6531</v>
+        <v>0.2721</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.955</v>
+        <v>-0.1177</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.698</v>
+        <v>0.3899</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>2.428</v>
+        <v>1.214</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8665</v>
+        <v>1.1167</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3619</v>
+        <v>1.5113</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4954</v>
+        <v>-0.3946</v>
       </c>
       <c r="G6" t="n">
         <v>2.0876</v>
@@ -922,13 +922,13 @@
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3087</v>
+        <v>-1.0585</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3848</v>
+        <v>-0.2355</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9238</v>
+        <v>-0.823</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7643</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0332</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7647</v>
+        <v>-0.7311</v>
       </c>
       <c r="G7" t="n">
         <v>0.4839</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6734</v>
+        <v>-0.6398</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6067</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.281</v>
+        <v>-1.4668</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3261</v>
+        <v>-0.0278</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.607</v>
+        <v>-1.439</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3984</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0452</v>
+        <v>-0.1406</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5034</v>
+        <v>0.1496</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4582</v>
+        <v>-0.2902</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7148</v>
+        <v>-1.496</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2455</v>
+        <v>-1.1275</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4693</v>
+        <v>-0.3685</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3181</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3967</v>
+        <v>-0.1779</v>
       </c>
       <c r="T9" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4046</v>
+        <v>-0.3038</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5773</v>
+        <v>-1.9732</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.264</v>
+        <v>-0.7608</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3132</v>
+        <v>-1.2124</v>
       </c>
       <c r="G10" t="n">
         <v>0.8269</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6207</v>
+        <v>-0.0167</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.507</v>
+        <v>-0.0037</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1138</v>
+        <v>-0.013</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8603</v>
+        <v>-4.6539</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8417</v>
+        <v>-1.4001</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0186</v>
+        <v>-3.2538</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9433</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0108</v>
+        <v>0.2172</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6256</v>
+        <v>0.0672</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3853</v>
+        <v>0.15</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3701</v>
+        <v>-6.8311</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0311</v>
+        <v>-6.5593</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.339</v>
+        <v>-0.2718</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8451</v>
@@ -1390,13 +1390,13 @@
         <v>2.3195</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9013</v>
+        <v>-1.3623</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8804</v>
+        <v>-0.4086</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0209</v>
+        <v>-0.9537</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.783200000000001</v>
+        <v>-6.036200000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>2.181700000000001</v>
+        <v>2.9284</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.964599999999999</v>
+        <v>-8.964800000000002</v>
       </c>
       <c r="G13" t="n">
         <v>1.105900000000001</v>
@@ -1468,13 +1468,13 @@
         <v>13.9171</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.798800000000001</v>
+        <v>-5.052</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4322</v>
+        <v>-0.6854</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.3666</v>
+        <v>-4.3667</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9303999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1113</v>
+        <v>8.970700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>8.218299999999999</v>
+        <v>9.515700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1069</v>
+        <v>-0.5451</v>
       </c>
       <c r="G14" t="n">
         <v>3.974</v>
@@ -1546,13 +1546,13 @@
         <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7055</v>
+        <v>1.1538</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.731</v>
+        <v>0.5665</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0255</v>
+        <v>0.5874</v>
       </c>
       <c r="V14" t="n">
         <v>3.6109</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9498</v>
+        <v>3.9978</v>
       </c>
       <c r="E15" t="n">
-        <v>3.361</v>
+        <v>2.7206</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5888</v>
+        <v>1.2772</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2543</v>
+        <v>0.3287</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7489</v>
+        <v>-1.3878</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5053</v>
+        <v>1.7165</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9729</v>
+        <v>1.6409</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9361</v>
+        <v>0.2324</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0368</v>
+        <v>1.4085</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7186</v>
+        <v>-1.3122</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1871</v>
+        <v>-1.6203</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4685</v>
+        <v>0.308</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0719</v>
+        <v>0.6871</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7799</v>
+        <v>0.1852</v>
       </c>
       <c r="U15" t="n">
-        <v>1.292</v>
+        <v>0.5019</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6083</v>
+        <v>2.2862</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9725</v>
+        <v>2.9268</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5773</v>
+        <v>3.6337</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6048</v>
+        <v>-0.7069</v>
       </c>
       <c r="G16" t="n">
         <v>1.7487</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3681</v>
+        <v>0.3224</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3961</v>
+        <v>0.4525</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.028</v>
+        <v>-0.13</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9369</v>
+        <v>1.996</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3667</v>
+        <v>1.7097</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5702</v>
+        <v>0.2863</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3287</v>
+        <v>1.2543</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3878</v>
+        <v>0.7489</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7165</v>
+        <v>0.5053</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6409</v>
+        <v>1.9729</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2324</v>
+        <v>1.9361</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4085</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3122</v>
+        <v>-0.7186</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6203</v>
+        <v>-1.1871</v>
       </c>
       <c r="O17" t="n">
-        <v>0.308</v>
+        <v>0.4685</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3738</v>
+        <v>2.1181</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1687</v>
+        <v>1.1286</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2051</v>
+        <v>0.9895</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2862</v>
+        <v>-1.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,22 +1813,22 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6006</v>
+        <v>-0.2961</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7695</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1689</v>
+        <v>0.2689</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6231</v>
+        <v>-0.6873</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6231</v>
+        <v>-0.7911</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1038</v>
       </c>
       <c r="J18" t="n">
         <v>-0.7695</v>
@@ -1840,31 +1840,31 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1465</v>
+        <v>0.0822</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1465</v>
+        <v>-0.0216</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.1038</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0224</v>
+        <v>0.1592</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.2045</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>-0.0452</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8704</v>
+        <v>-0.4491</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.6516</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7742</v>
+        <v>0.2025</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5282</v>
+        <v>-0.6231</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6387</v>
+        <v>-0.6231</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1105</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2554</v>
+        <v>-0.7695</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0077</v>
+        <v>-0.7695</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2728</v>
+        <v>0.1465</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.631</v>
+        <v>0.1465</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3583</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9439</v>
+        <v>0.174</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2467</v>
+        <v>0.118</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6972</v>
+        <v>0.056</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.6372</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0444</v>
+        <v>0.4523</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6873</v>
+        <v>-1.6889</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7911</v>
+        <v>-1.0264</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1038</v>
+        <v>-0.6625</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7695</v>
+        <v>-0.8773</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7695</v>
+        <v>-0.1646</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.7127</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0822</v>
+        <v>-0.8116</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0216</v>
+        <v>-0.8618</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1038</v>
+        <v>0.0502</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4191</v>
+        <v>0.3558</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>0.0198</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2697</v>
+        <v>0.3361</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0106</v>
+        <v>-0.6625</v>
       </c>
       <c r="E21" t="n">
         <v>-1.0152</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0046</v>
+        <v>0.3527</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5232</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8167</v>
+        <v>1.1648</v>
       </c>
       <c r="T21" t="n">
         <v>0.8338</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0171</v>
+        <v>0.331</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0747</v>
+        <v>-0.734</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3254</v>
+        <v>0.4951</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2507</v>
+        <v>-1.229</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6889</v>
+        <v>-0.1317</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0264</v>
+        <v>-2.9123</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6625</v>
+        <v>2.7806</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8773</v>
+        <v>0.7905</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1646</v>
+        <v>-1.3675</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7127</v>
+        <v>2.1581</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8116</v>
+        <v>-0.9222</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8618</v>
+        <v>-1.5448</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0502</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.5601</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2161</v>
+        <v>-0.1177</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1344</v>
+        <v>0.6778</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3187</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0232</v>
+        <v>-0.3321</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3419</v>
+        <v>-0.6492</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1317</v>
+        <v>-2.5282</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.9123</v>
+        <v>-2.6387</v>
       </c>
       <c r="I23" t="n">
-        <v>2.7806</v>
+        <v>0.1105</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7905</v>
+        <v>-1.2554</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3675</v>
+        <v>-1.0077</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1581</v>
+        <v>-0.2477</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9222</v>
+        <v>-1.2728</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5448</v>
+        <v>-1.631</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.3583</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0246</v>
+        <v>1.833</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5895</v>
+        <v>1.0108</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5649</v>
+        <v>0.8222</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9304</v>
+        <v>-1.214</v>
       </c>
       <c r="W23" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1444</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5394</v>
+        <v>-1.1019</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4009</v>
+        <v>-1.165</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1386</v>
+        <v>0.0631</v>
       </c>
       <c r="G24" t="n">
         <v>0.9419</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3216</v>
+        <v>0.116</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0228</v>
+        <v>0.1788</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8983</v>
+        <v>-2.9827</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9835</v>
+        <v>-3.1015</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0852</v>
+        <v>0.1188</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1711</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5021</v>
+        <v>0.4178</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2385</v>
+        <v>0.2721</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1418</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.783300000000001</v>
+        <v>10.0464</v>
       </c>
       <c r="E26" t="n">
-        <v>10.0369</v>
+        <v>10.1549</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2536</v>
+        <v>-0.1084000000000002</v>
       </c>
       <c r="G26" t="n">
         <v>-1.105900000000001</v>
@@ -2458,7 +2458,7 @@
         <v>10.0484</v>
       </c>
       <c r="K26" t="n">
-        <v>6.3352</v>
+        <v>6.335200000000001</v>
       </c>
       <c r="L26" t="n">
         <v>3.7132</v>
@@ -2482,13 +2482,13 @@
         <v>15.0771</v>
       </c>
       <c r="S26" t="n">
-        <v>5.7988</v>
+        <v>9.062099999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>4.3667</v>
+        <v>4.4848</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4322</v>
+        <v>4.5776</v>
       </c>
       <c r="V26" t="n">
         <v>0.9303999999999998</v>
